--- a/data/trans_dic/IP43-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP43-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones</t>
+          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,43; 25,47</t>
+          <t>14,4; 24,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 20,18</t>
+          <t>10,17; 19,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 28,71</t>
+          <t>17,5; 29,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 21,32</t>
+          <t>10,38; 20,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,28; 25,17</t>
+          <t>17,29; 24,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,65; 18,92</t>
+          <t>11,68; 18,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,46; 28,23</t>
+          <t>19,68; 28,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 16,69</t>
+          <t>9,5; 16,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,13; 28,81</t>
+          <t>19,39; 28,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 13,79</t>
+          <t>7,09; 13,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,63; 27,02</t>
+          <t>20,85; 27,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 13,68</t>
+          <t>9,03; 13,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,04; 33,14</t>
+          <t>20,74; 32,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 12,64</t>
+          <t>6,42; 13,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 29,09</t>
+          <t>18,91; 30,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 13,6</t>
+          <t>6,47; 13,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,21; 29,41</t>
+          <t>21,3; 29,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 11,92</t>
+          <t>7,28; 12,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 27,65</t>
+          <t>16,89; 27,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 18,66</t>
+          <t>9,42; 18,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 28,17</t>
+          <t>18,02; 28,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 17,76</t>
+          <t>9,09; 17,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,68; 26,23</t>
+          <t>18,64; 26,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 16,31</t>
+          <t>10,48; 16,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,17; 25,2</t>
+          <t>20,46; 25,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,65; 14,33</t>
+          <t>10,69; 14,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,9; 25,8</t>
+          <t>20,92; 25,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 13,47</t>
+          <t>9,68; 13,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,44; 24,93</t>
+          <t>21,44; 25,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 13,23</t>
+          <t>10,61; 13,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aceptaría ser contactado para participar en futuras investigaciones (tasa de respuesta: 99,69%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>28120</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18958</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32942</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19195</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61063</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>38153</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>21047; 36107</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13389; 26192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25420; 42332</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12894; 25493</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>50385; 72702</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>29885; 47551</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>54955</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26993</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>63358</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25985</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>118313</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>52978</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>45766; 67162</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19991; 35266</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>51495; 75746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>18305; 34218</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>103891; 135535</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>42294; 64306</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>40895</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17304</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37517</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17993</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78412</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>35297</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>32391; 50093</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12129; 24686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>29867; 47890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12202; 25097</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>66893; 92047</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>27471; 45527</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>36961</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23564</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40552</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22160</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77513</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>45724</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>28829; 46842</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16333; 32207</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31980; 50441</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15819; 30829</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>64885; 91057</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>36387; 57999</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>160932</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>86819</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>174370</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85333</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>335301</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>172152</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>144375; 180570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>75310; 103074</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>156126; 193207</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>72087; 100281</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>311265; 363281</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>153793; 193495</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>